--- a/artfynd/A 20722-2024 artfynd.xlsx
+++ b/artfynd/A 20722-2024 artfynd.xlsx
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117938580</v>
+        <v>117939430</v>
       </c>
       <c r="B3" t="n">
-        <v>97836</v>
+        <v>90517</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,47 +810,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692535</v>
+        <v>692467</v>
       </c>
       <c r="R3" t="n">
-        <v>6635930</v>
+        <v>6635836</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,19 +871,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,22 +888,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117937314</v>
+        <v>117939282</v>
       </c>
       <c r="B4" t="n">
-        <v>97836</v>
+        <v>57303</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,50 +912,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>692583</v>
+        <v>692487</v>
       </c>
       <c r="R4" t="n">
-        <v>6635986</v>
+        <v>6635864</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,19 +978,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,22 +995,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117941737</v>
+        <v>117938580</v>
       </c>
       <c r="B5" t="n">
-        <v>100097</v>
+        <v>97836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,38 +1019,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>692563</v>
+        <v>692535</v>
       </c>
       <c r="R5" t="n">
-        <v>6635887</v>
+        <v>6635930</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,9 +1089,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,22 +1116,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117939430</v>
+        <v>117937314</v>
       </c>
       <c r="B6" t="n">
-        <v>90517</v>
+        <v>97836</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,41 +1140,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>692467</v>
+        <v>692583</v>
       </c>
       <c r="R6" t="n">
-        <v>6635836</v>
+        <v>6635986</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,9 +1210,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,22 +1237,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117939282</v>
+        <v>117941737</v>
       </c>
       <c r="B7" t="n">
-        <v>57303</v>
+        <v>100097</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,43 +1261,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>692487</v>
+        <v>692563</v>
       </c>
       <c r="R7" t="n">
-        <v>6635864</v>
+        <v>6635887</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117937784</v>
+        <v>117938005</v>
       </c>
       <c r="B19" t="n">
-        <v>97836</v>
+        <v>57768</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2641,55 +2641,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103018</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>692568</v>
+        <v>692578</v>
       </c>
       <c r="R19" t="n">
-        <v>6635991</v>
+        <v>6635954</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2716,24 +2702,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2748,22 +2719,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117938005</v>
+        <v>117937784</v>
       </c>
       <c r="B20" t="n">
-        <v>57768</v>
+        <v>97836</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2772,41 +2743,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103018</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>692578</v>
+        <v>692568</v>
       </c>
       <c r="R20" t="n">
-        <v>6635954</v>
+        <v>6635991</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2833,9 +2818,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2850,12 +2850,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3225,10 +3225,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117941966</v>
+        <v>117937975</v>
       </c>
       <c r="B24" t="n">
-        <v>97836</v>
+        <v>57303</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3237,40 +3237,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3279,10 +3270,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>692578</v>
+        <v>692575</v>
       </c>
       <c r="R24" t="n">
-        <v>6635898</v>
+        <v>6635954</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3341,10 +3332,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117938431</v>
+        <v>117937862</v>
       </c>
       <c r="B25" t="n">
-        <v>97836</v>
+        <v>5186</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3353,50 +3344,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>692527</v>
+        <v>692594</v>
       </c>
       <c r="R25" t="n">
-        <v>6635949</v>
+        <v>6635976</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3423,49 +3414,40 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117937975</v>
+        <v>117938431</v>
       </c>
       <c r="B26" t="n">
-        <v>57303</v>
+        <v>97836</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3474,46 +3456,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>692575</v>
+        <v>692527</v>
       </c>
       <c r="R26" t="n">
-        <v>6635954</v>
+        <v>6635949</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3540,9 +3526,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3557,22 +3553,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117937862</v>
+        <v>117941966</v>
       </c>
       <c r="B27" t="n">
-        <v>5186</v>
+        <v>97836</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3581,47 +3577,52 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>692594</v>
+        <v>692578</v>
       </c>
       <c r="R27" t="n">
-        <v>6635976</v>
+        <v>6635898</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3662,7 +3663,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -8567,10 +8567,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117940793</v>
+        <v>117938213</v>
       </c>
       <c r="B70" t="n">
-        <v>5166</v>
+        <v>97836</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8579,50 +8579,50 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>692434</v>
+        <v>692555</v>
       </c>
       <c r="R70" t="n">
-        <v>6635779</v>
+        <v>6635951</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8649,37 +8649,51 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>4 med knoppig blomstängel tv</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117938213</v>
+        <v>117939029</v>
       </c>
       <c r="B71" t="n">
         <v>97836</v>
@@ -8714,7 +8728,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8722,19 +8736,24 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>692555</v>
+        <v>692506</v>
       </c>
       <c r="R71" t="n">
-        <v>6635951</v>
+        <v>6635887</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8761,24 +8780,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>4 med knoppig blomstängel tv</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8793,22 +8797,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117939029</v>
+        <v>117940793</v>
       </c>
       <c r="B72" t="n">
-        <v>97836</v>
+        <v>5166</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8817,52 +8821,47 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>692506</v>
+        <v>692434</v>
       </c>
       <c r="R72" t="n">
-        <v>6635887</v>
+        <v>6635779</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8903,6 +8902,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20722-2024 artfynd.xlsx
+++ b/artfynd/A 20722-2024 artfynd.xlsx
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117939430</v>
+        <v>117939183</v>
       </c>
       <c r="B3" t="n">
-        <v>90517</v>
+        <v>97836</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,38 +810,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692467</v>
+        <v>692452</v>
       </c>
       <c r="R3" t="n">
-        <v>6635836</v>
+        <v>6635944</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,9 +880,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,22 +907,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117939282</v>
+        <v>117937992</v>
       </c>
       <c r="B4" t="n">
-        <v>57303</v>
+        <v>97836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,31 +931,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -945,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>692487</v>
+        <v>692573</v>
       </c>
       <c r="R4" t="n">
-        <v>6635864</v>
+        <v>6635954</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117938580</v>
+        <v>117938795</v>
       </c>
       <c r="B5" t="n">
         <v>97836</v>
@@ -1042,7 +1070,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1050,16 +1078,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>692535</v>
+        <v>692508</v>
       </c>
       <c r="R5" t="n">
-        <v>6635930</v>
+        <v>6635905</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,19 +1122,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1139,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117937314</v>
+        <v>117941899</v>
       </c>
       <c r="B6" t="n">
-        <v>97836</v>
+        <v>90499</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,50 +1163,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>692583</v>
+        <v>692580</v>
       </c>
       <c r="R6" t="n">
-        <v>6635986</v>
+        <v>6635891</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,19 +1224,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,22 +1241,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117941737</v>
+        <v>117938933</v>
       </c>
       <c r="B7" t="n">
-        <v>100097</v>
+        <v>97836</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,38 +1265,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>692563</v>
+        <v>692516</v>
       </c>
       <c r="R7" t="n">
-        <v>6635887</v>
+        <v>6635890</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,7 +1369,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117942312</v>
+        <v>117942210</v>
       </c>
       <c r="B8" t="n">
         <v>97836</v>
@@ -1386,7 +1404,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1405,10 +1423,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>692611</v>
+        <v>692602</v>
       </c>
       <c r="R8" t="n">
-        <v>6635972</v>
+        <v>6635953</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,10 +1485,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117939646</v>
+        <v>117939212</v>
       </c>
       <c r="B9" t="n">
-        <v>5186</v>
+        <v>97836</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,47 +1497,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>692415</v>
+        <v>692482</v>
       </c>
       <c r="R9" t="n">
-        <v>6635846</v>
+        <v>6635862</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,7 +1583,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1579,7 +1601,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117941596</v>
+        <v>117939096</v>
       </c>
       <c r="B10" t="n">
         <v>97836</v>
@@ -1614,7 +1636,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1628,10 +1650,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>692474</v>
+        <v>692535</v>
       </c>
       <c r="R10" t="n">
-        <v>6635824</v>
+        <v>6635930</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1673,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117941687</v>
+        <v>117939430</v>
       </c>
       <c r="B11" t="n">
-        <v>97836</v>
+        <v>90517</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,52 +1734,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>692553</v>
+        <v>692467</v>
       </c>
       <c r="R11" t="n">
-        <v>6635890</v>
+        <v>6635836</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1816,7 +1824,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117941471</v>
+        <v>117938174</v>
       </c>
       <c r="B12" t="n">
         <v>97836</v>
@@ -1851,7 +1859,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1859,16 +1867,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>692463</v>
+        <v>692551</v>
       </c>
       <c r="R12" t="n">
-        <v>6635816</v>
+        <v>6635923</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1898,19 +1911,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,19 +1928,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117937256</v>
+        <v>117942112</v>
       </c>
       <c r="B13" t="n">
         <v>97836</v>
@@ -1972,7 +1975,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1980,21 +1983,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>692608</v>
+        <v>692538</v>
       </c>
       <c r="R13" t="n">
-        <v>6635981</v>
+        <v>6635877</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,9 +2022,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,19 +2054,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117941752</v>
+        <v>117938975</v>
       </c>
       <c r="B14" t="n">
         <v>97836</v>
@@ -2088,7 +2101,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2107,10 +2120,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>692560</v>
+        <v>692514</v>
       </c>
       <c r="R14" t="n">
-        <v>6635889</v>
+        <v>6635894</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2169,10 +2182,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117939062</v>
+        <v>117937314</v>
       </c>
       <c r="B15" t="n">
-        <v>5166</v>
+        <v>97836</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,46 +2194,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>692498</v>
+        <v>692583</v>
       </c>
       <c r="R15" t="n">
-        <v>6635884</v>
+        <v>6635986</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2247,9 +2264,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,19 +2291,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117939187</v>
+        <v>117939347</v>
       </c>
       <c r="B16" t="n">
         <v>97836</v>
@@ -2311,7 +2338,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2319,21 +2346,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>692474</v>
+        <v>692449</v>
       </c>
       <c r="R16" t="n">
-        <v>6635872</v>
+        <v>6635952</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,9 +2385,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Två med knoppiga blomstänglar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,22 +2417,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117937381</v>
+        <v>117940804</v>
       </c>
       <c r="B17" t="n">
-        <v>97836</v>
+        <v>5186</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2404,50 +2441,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>692597</v>
+        <v>692436</v>
       </c>
       <c r="R17" t="n">
-        <v>6635979</v>
+        <v>6635782</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2474,46 +2511,37 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117937927</v>
+        <v>117938588</v>
       </c>
       <c r="B18" t="n">
         <v>97836</v>
@@ -2548,7 +2576,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2558,7 +2586,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2567,10 +2595,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>692577</v>
+        <v>692521</v>
       </c>
       <c r="R18" t="n">
-        <v>6635977</v>
+        <v>6635907</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2629,10 +2657,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117938005</v>
+        <v>117941687</v>
       </c>
       <c r="B19" t="n">
-        <v>57768</v>
+        <v>97836</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2641,38 +2669,52 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103018</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>692578</v>
+        <v>692553</v>
       </c>
       <c r="R19" t="n">
-        <v>6635954</v>
+        <v>6635890</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2731,7 +2773,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117937784</v>
+        <v>117937690</v>
       </c>
       <c r="B20" t="n">
         <v>97836</v>
@@ -2766,7 +2808,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2774,21 +2816,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>692568</v>
+        <v>692585</v>
       </c>
       <c r="R20" t="n">
-        <v>6635991</v>
+        <v>6635997</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2820,7 +2857,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2830,12 +2867,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,7 +2894,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117937995</v>
+        <v>117937555</v>
       </c>
       <c r="B21" t="n">
         <v>97836</v>
@@ -2897,7 +2929,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2905,19 +2937,24 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>692584</v>
+        <v>692599</v>
       </c>
       <c r="R21" t="n">
-        <v>6635955</v>
+        <v>6635973</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2944,19 +2981,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2971,22 +2998,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117939088</v>
+        <v>117938026</v>
       </c>
       <c r="B22" t="n">
-        <v>97836</v>
+        <v>57303</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2995,40 +3022,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3037,10 +3055,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>692498</v>
+        <v>692573</v>
       </c>
       <c r="R22" t="n">
-        <v>6635884</v>
+        <v>6635947</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3099,7 +3117,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117941678</v>
+        <v>117937256</v>
       </c>
       <c r="B23" t="n">
         <v>97836</v>
@@ -3134,7 +3152,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3142,16 +3160,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>692496</v>
+        <v>692608</v>
       </c>
       <c r="R23" t="n">
-        <v>6635822</v>
+        <v>6635981</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3181,24 +3204,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3213,22 +3221,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117937975</v>
+        <v>117937556</v>
       </c>
       <c r="B24" t="n">
-        <v>57303</v>
+        <v>97836</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3237,46 +3245,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>692575</v>
+        <v>692602</v>
       </c>
       <c r="R24" t="n">
-        <v>6635954</v>
+        <v>6635995</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3303,9 +3315,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,22 +3347,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117937862</v>
+        <v>117942312</v>
       </c>
       <c r="B25" t="n">
-        <v>5186</v>
+        <v>97836</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3344,47 +3371,52 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>692594</v>
+        <v>692611</v>
       </c>
       <c r="R25" t="n">
-        <v>6635976</v>
+        <v>6635972</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3425,7 +3457,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3444,7 +3475,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117938431</v>
+        <v>117939029</v>
       </c>
       <c r="B26" t="n">
         <v>97836</v>
@@ -3479,7 +3510,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3487,19 +3518,24 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>692527</v>
+        <v>692506</v>
       </c>
       <c r="R26" t="n">
-        <v>6635949</v>
+        <v>6635887</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3526,19 +3562,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3553,19 +3579,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117941966</v>
+        <v>117937381</v>
       </c>
       <c r="B27" t="n">
         <v>97836</v>
@@ -3600,7 +3626,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3608,24 +3634,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>692578</v>
+        <v>692597</v>
       </c>
       <c r="R27" t="n">
-        <v>6635898</v>
+        <v>6635979</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3652,9 +3673,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3669,22 +3700,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117940804</v>
+        <v>117937927</v>
       </c>
       <c r="B28" t="n">
-        <v>5186</v>
+        <v>97836</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3693,47 +3724,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>692436</v>
+        <v>692577</v>
       </c>
       <c r="R28" t="n">
-        <v>6635782</v>
+        <v>6635977</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3774,7 +3810,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3793,10 +3828,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117941899</v>
+        <v>117938005</v>
       </c>
       <c r="B29" t="n">
-        <v>90499</v>
+        <v>57768</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3809,21 +3844,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>103018</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3833,10 +3868,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>692580</v>
+        <v>692578</v>
       </c>
       <c r="R29" t="n">
-        <v>6635891</v>
+        <v>6635954</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3895,10 +3930,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117942921</v>
+        <v>117938213</v>
       </c>
       <c r="B30" t="n">
-        <v>5166</v>
+        <v>97836</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3907,41 +3942,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön, Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>692583</v>
+        <v>692555</v>
       </c>
       <c r="R30" t="n">
-        <v>6635986</v>
+        <v>6635951</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3970,7 +4014,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3980,7 +4024,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>4 med knoppig blomstängel tv</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4007,7 +4056,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117938311</v>
+        <v>117941641</v>
       </c>
       <c r="B31" t="n">
         <v>97836</v>
@@ -4042,7 +4091,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4050,19 +4099,24 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>692539</v>
+        <v>692543</v>
       </c>
       <c r="R31" t="n">
-        <v>6635922</v>
+        <v>6635857</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4089,24 +4143,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4121,19 +4160,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117937309</v>
+        <v>117941966</v>
       </c>
       <c r="B32" t="n">
         <v>97836</v>
@@ -4168,7 +4207,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4178,19 +4217,19 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>692610</v>
+        <v>692578</v>
       </c>
       <c r="R32" t="n">
-        <v>6635980</v>
+        <v>6635898</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4220,19 +4259,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4259,10 +4288,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117937630</v>
+        <v>117937975</v>
       </c>
       <c r="B33" t="n">
-        <v>97836</v>
+        <v>57303</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4271,52 +4300,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sjöstugan (Sjöstugan), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>692596</v>
+        <v>692575</v>
       </c>
       <c r="R33" t="n">
-        <v>6635973</v>
+        <v>6635954</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4375,10 +4395,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117938933</v>
+        <v>117939282</v>
       </c>
       <c r="B34" t="n">
-        <v>97836</v>
+        <v>57303</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4387,40 +4407,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4429,10 +4440,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>692516</v>
+        <v>692487</v>
       </c>
       <c r="R34" t="n">
-        <v>6635890</v>
+        <v>6635864</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4491,10 +4502,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117942112</v>
+        <v>117939062</v>
       </c>
       <c r="B35" t="n">
-        <v>97836</v>
+        <v>5166</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4503,47 +4514,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>692538</v>
+        <v>692498</v>
       </c>
       <c r="R35" t="n">
-        <v>6635877</v>
+        <v>6635884</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4573,24 +4580,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4605,22 +4597,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117942036</v>
+        <v>117941342</v>
       </c>
       <c r="B36" t="n">
-        <v>97836</v>
+        <v>5166</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4629,52 +4621,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>692568</v>
+        <v>692449</v>
       </c>
       <c r="R36" t="n">
-        <v>6635907</v>
+        <v>6635786</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4704,9 +4682,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4721,22 +4709,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117939581</v>
+        <v>117941471</v>
       </c>
       <c r="B37" t="n">
-        <v>57303</v>
+        <v>97836</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4745,43 +4733,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>692448</v>
+        <v>692463</v>
       </c>
       <c r="R37" t="n">
-        <v>6635840</v>
+        <v>6635816</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4811,9 +4803,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4828,19 +4830,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117938078</v>
+        <v>117937784</v>
       </c>
       <c r="B38" t="n">
         <v>97836</v>
@@ -4875,7 +4877,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4885,22 +4887,22 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>692569</v>
+        <v>692568</v>
       </c>
       <c r="R38" t="n">
-        <v>6635939</v>
+        <v>6635991</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4927,9 +4929,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4944,22 +4961,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117938132</v>
+        <v>117941545</v>
       </c>
       <c r="B39" t="n">
-        <v>97836</v>
+        <v>57303</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4968,40 +4985,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5010,10 +5018,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>692562</v>
+        <v>692519</v>
       </c>
       <c r="R39" t="n">
-        <v>6635932</v>
+        <v>6635833</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5072,10 +5080,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117937757</v>
+        <v>117937862</v>
       </c>
       <c r="B40" t="n">
-        <v>97836</v>
+        <v>5186</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5084,52 +5092,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>692596</v>
+        <v>692594</v>
       </c>
       <c r="R40" t="n">
-        <v>6635955</v>
+        <v>6635976</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5170,6 +5173,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5188,10 +5192,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117939070</v>
+        <v>117939382</v>
       </c>
       <c r="B41" t="n">
-        <v>5186</v>
+        <v>97836</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5200,31 +5204,40 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5233,10 +5246,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>692498</v>
+        <v>692463</v>
       </c>
       <c r="R41" t="n">
-        <v>6635884</v>
+        <v>6635839</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5295,7 +5308,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117941588</v>
+        <v>117937630</v>
       </c>
       <c r="B42" t="n">
         <v>97836</v>
@@ -5330,7 +5343,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5340,19 +5353,19 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Sjöstugan (Sjöstugan), Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>692530</v>
+        <v>692596</v>
       </c>
       <c r="R42" t="n">
-        <v>6635831</v>
+        <v>6635973</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5411,7 +5424,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117938795</v>
+        <v>117942036</v>
       </c>
       <c r="B43" t="n">
         <v>97836</v>
@@ -5446,7 +5459,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5465,10 +5478,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>692508</v>
+        <v>692568</v>
       </c>
       <c r="R43" t="n">
-        <v>6635905</v>
+        <v>6635907</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5527,7 +5540,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117938225</v>
+        <v>117941588</v>
       </c>
       <c r="B44" t="n">
         <v>97836</v>
@@ -5562,7 +5575,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5581,10 +5594,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>692543</v>
+        <v>692530</v>
       </c>
       <c r="R44" t="n">
-        <v>6635916</v>
+        <v>6635831</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5643,7 +5656,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117941641</v>
+        <v>117937494</v>
       </c>
       <c r="B45" t="n">
         <v>97836</v>
@@ -5678,7 +5691,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5693,14 +5706,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>692543</v>
+        <v>692606</v>
       </c>
       <c r="R45" t="n">
-        <v>6635857</v>
+        <v>6635979</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5730,9 +5743,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5759,7 +5782,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117941865</v>
+        <v>117942075</v>
       </c>
       <c r="B46" t="n">
         <v>97836</v>
@@ -5794,7 +5817,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5802,16 +5825,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>692513</v>
+        <v>692570</v>
       </c>
       <c r="R46" t="n">
-        <v>6635854</v>
+        <v>6635906</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5841,24 +5869,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5873,22 +5886,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117941545</v>
+        <v>117941865</v>
       </c>
       <c r="B47" t="n">
-        <v>57303</v>
+        <v>97836</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5897,43 +5910,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>692519</v>
+        <v>692513</v>
       </c>
       <c r="R47" t="n">
-        <v>6635833</v>
+        <v>6635854</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5963,9 +5980,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5980,19 +6012,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117937690</v>
+        <v>117937214</v>
       </c>
       <c r="B48" t="n">
         <v>97836</v>
@@ -6027,7 +6059,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6035,19 +6067,24 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön (Sjöstugan), Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>692585</v>
+        <v>692607</v>
       </c>
       <c r="R48" t="n">
-        <v>6635997</v>
+        <v>6635979</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6074,19 +6111,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6101,22 +6128,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117941484</v>
+        <v>117938311</v>
       </c>
       <c r="B49" t="n">
-        <v>90517</v>
+        <v>97836</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6125,41 +6152,50 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>692520</v>
+        <v>692539</v>
       </c>
       <c r="R49" t="n">
-        <v>6635829</v>
+        <v>6635922</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6186,9 +6222,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6203,19 +6254,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117939183</v>
+        <v>117937309</v>
       </c>
       <c r="B50" t="n">
         <v>97836</v>
@@ -6250,7 +6301,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6258,16 +6309,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>692452</v>
+        <v>692610</v>
       </c>
       <c r="R50" t="n">
-        <v>6635944</v>
+        <v>6635980</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6299,7 +6355,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6309,7 +6365,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6324,19 +6380,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117937494</v>
+        <v>117938132</v>
       </c>
       <c r="B51" t="n">
         <v>97836</v>
@@ -6371,7 +6427,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6386,14 +6442,14 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>692606</v>
+        <v>692562</v>
       </c>
       <c r="R51" t="n">
-        <v>6635979</v>
+        <v>6635932</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6423,19 +6479,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:42</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6462,7 +6508,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117937556</v>
+        <v>117939088</v>
       </c>
       <c r="B52" t="n">
         <v>97836</v>
@@ -6497,7 +6543,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6505,19 +6551,24 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>692602</v>
+        <v>692498</v>
       </c>
       <c r="R52" t="n">
-        <v>6635995</v>
+        <v>6635884</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6544,24 +6595,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6576,19 +6612,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117942075</v>
+        <v>117937938</v>
       </c>
       <c r="B53" t="n">
         <v>97836</v>
@@ -6623,7 +6659,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6631,24 +6667,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>692570</v>
+        <v>692549</v>
       </c>
       <c r="R53" t="n">
-        <v>6635906</v>
+        <v>6635965</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6675,9 +6706,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6692,19 +6733,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117938588</v>
+        <v>117938431</v>
       </c>
       <c r="B54" t="n">
         <v>97836</v>
@@ -6739,7 +6780,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6747,24 +6788,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>692521</v>
+        <v>692527</v>
       </c>
       <c r="R54" t="n">
-        <v>6635907</v>
+        <v>6635949</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6791,9 +6827,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6808,19 +6854,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117937628</v>
+        <v>117941596</v>
       </c>
       <c r="B55" t="n">
         <v>97836</v>
@@ -6855,7 +6901,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6869,13 +6915,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>692583</v>
+        <v>692474</v>
       </c>
       <c r="R55" t="n">
-        <v>6635987</v>
+        <v>6635824</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6904,7 +6950,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6914,12 +6960,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6946,10 +6987,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117939382</v>
+        <v>117942921</v>
       </c>
       <c r="B56" t="n">
-        <v>97836</v>
+        <v>5166</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6958,55 +6999,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>692463</v>
+        <v>692583</v>
       </c>
       <c r="R56" t="n">
-        <v>6635839</v>
+        <v>6635986</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7033,9 +7060,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7050,22 +7087,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117938975</v>
+        <v>117940793</v>
       </c>
       <c r="B57" t="n">
-        <v>97836</v>
+        <v>5166</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7074,52 +7111,47 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>692514</v>
+        <v>692434</v>
       </c>
       <c r="R57" t="n">
-        <v>6635894</v>
+        <v>6635779</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7160,6 +7192,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7178,10 +7211,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117938026</v>
+        <v>117939646</v>
       </c>
       <c r="B58" t="n">
-        <v>57303</v>
+        <v>5186</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7190,20 +7223,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -7212,21 +7245,25 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>692573</v>
+        <v>692415</v>
       </c>
       <c r="R58" t="n">
-        <v>6635947</v>
+        <v>6635846</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7267,6 +7304,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7285,10 +7323,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117940890</v>
+        <v>117939581</v>
       </c>
       <c r="B59" t="n">
-        <v>97836</v>
+        <v>57303</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7297,40 +7335,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7339,10 +7368,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>692459</v>
+        <v>692448</v>
       </c>
       <c r="R59" t="n">
-        <v>6635787</v>
+        <v>6635840</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7401,10 +7430,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117937938</v>
+        <v>117941484</v>
       </c>
       <c r="B60" t="n">
-        <v>97836</v>
+        <v>90517</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7413,50 +7442,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>692549</v>
+        <v>692520</v>
       </c>
       <c r="R60" t="n">
-        <v>6635965</v>
+        <v>6635829</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7483,19 +7503,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7510,22 +7520,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117941342</v>
+        <v>117940890</v>
       </c>
       <c r="B61" t="n">
-        <v>5166</v>
+        <v>97836</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7534,38 +7544,52 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>692449</v>
+        <v>692459</v>
       </c>
       <c r="R61" t="n">
-        <v>6635786</v>
+        <v>6635787</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7595,19 +7619,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7622,22 +7636,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117937214</v>
+        <v>117941737</v>
       </c>
       <c r="B62" t="n">
-        <v>97836</v>
+        <v>100097</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7646,52 +7660,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön (Sjöstugan), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>692607</v>
+        <v>692563</v>
       </c>
       <c r="R62" t="n">
-        <v>6635979</v>
+        <v>6635887</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7750,7 +7750,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117942210</v>
+        <v>117938078</v>
       </c>
       <c r="B63" t="n">
         <v>97836</v>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7804,10 +7804,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>692602</v>
+        <v>692569</v>
       </c>
       <c r="R63" t="n">
-        <v>6635953</v>
+        <v>6635939</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7866,7 +7866,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117938174</v>
+        <v>117937995</v>
       </c>
       <c r="B64" t="n">
         <v>97836</v>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7909,24 +7909,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>692551</v>
+        <v>692584</v>
       </c>
       <c r="R64" t="n">
-        <v>6635923</v>
+        <v>6635955</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7953,9 +7948,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7970,19 +7975,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117939275</v>
+        <v>117938661</v>
       </c>
       <c r="B65" t="n">
         <v>97836</v>
@@ -8017,7 +8022,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8025,16 +8030,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>692449</v>
+        <v>692521</v>
       </c>
       <c r="R65" t="n">
-        <v>6635952</v>
+        <v>6635910</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8064,19 +8074,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>12:48</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8091,19 +8091,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117939212</v>
+        <v>117941678</v>
       </c>
       <c r="B66" t="n">
         <v>97836</v>
@@ -8146,21 +8146,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>692482</v>
+        <v>692496</v>
       </c>
       <c r="R66" t="n">
-        <v>6635862</v>
+        <v>6635822</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8190,9 +8185,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8207,19 +8217,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117937555</v>
+        <v>117937628</v>
       </c>
       <c r="B67" t="n">
         <v>97836</v>
@@ -8254,7 +8264,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8262,24 +8272,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>692599</v>
+        <v>692583</v>
       </c>
       <c r="R67" t="n">
-        <v>6635973</v>
+        <v>6635987</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8306,9 +8311,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8323,19 +8343,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117938661</v>
+        <v>117939187</v>
       </c>
       <c r="B68" t="n">
         <v>97836</v>
@@ -8370,7 +8390,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8389,10 +8409,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>692521</v>
+        <v>692474</v>
       </c>
       <c r="R68" t="n">
-        <v>6635910</v>
+        <v>6635872</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8451,7 +8471,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117937992</v>
+        <v>117938225</v>
       </c>
       <c r="B69" t="n">
         <v>97836</v>
@@ -8486,7 +8506,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8505,10 +8525,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>692573</v>
+        <v>692543</v>
       </c>
       <c r="R69" t="n">
-        <v>6635954</v>
+        <v>6635916</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8567,7 +8587,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117938213</v>
+        <v>117937757</v>
       </c>
       <c r="B70" t="n">
         <v>97836</v>
@@ -8602,7 +8622,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8610,19 +8630,24 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>692555</v>
+        <v>692596</v>
       </c>
       <c r="R70" t="n">
-        <v>6635951</v>
+        <v>6635955</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8649,24 +8674,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>4 med knoppig blomstängel tv</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8681,22 +8691,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117939029</v>
+        <v>117939070</v>
       </c>
       <c r="B71" t="n">
-        <v>97836</v>
+        <v>5186</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8705,40 +8715,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8747,10 +8748,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>692506</v>
+        <v>692498</v>
       </c>
       <c r="R71" t="n">
-        <v>6635887</v>
+        <v>6635884</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8809,10 +8810,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117940793</v>
+        <v>117941752</v>
       </c>
       <c r="B72" t="n">
-        <v>5166</v>
+        <v>97836</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8821,47 +8822,52 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>692434</v>
+        <v>692560</v>
       </c>
       <c r="R72" t="n">
-        <v>6635779</v>
+        <v>6635889</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8902,7 +8908,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20722-2024 artfynd.xlsx
+++ b/artfynd/A 20722-2024 artfynd.xlsx
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117939183</v>
+        <v>117938136</v>
       </c>
       <c r="B3" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692452</v>
+        <v>692583</v>
       </c>
       <c r="R3" t="n">
-        <v>6635944</v>
+        <v>6635986</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117937992</v>
+        <v>117941687</v>
       </c>
       <c r="B4" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>692573</v>
+        <v>692553</v>
       </c>
       <c r="R4" t="n">
-        <v>6635954</v>
+        <v>6635890</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117938795</v>
+        <v>117939088</v>
       </c>
       <c r="B5" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>692508</v>
+        <v>692498</v>
       </c>
       <c r="R5" t="n">
-        <v>6635905</v>
+        <v>6635884</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117941899</v>
+        <v>117937938</v>
       </c>
       <c r="B6" t="n">
-        <v>90499</v>
+        <v>97838</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,41 +1163,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>692580</v>
+        <v>692549</v>
       </c>
       <c r="R6" t="n">
-        <v>6635891</v>
+        <v>6635965</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,9 +1233,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,22 +1260,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117938933</v>
+        <v>117941752</v>
       </c>
       <c r="B7" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,7 +1307,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1307,10 +1326,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>692516</v>
+        <v>692560</v>
       </c>
       <c r="R7" t="n">
-        <v>6635890</v>
+        <v>6635889</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1369,10 +1388,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117942210</v>
+        <v>117937862</v>
       </c>
       <c r="B8" t="n">
-        <v>97836</v>
+        <v>5186</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,52 +1400,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>692602</v>
+        <v>692594</v>
       </c>
       <c r="R8" t="n">
-        <v>6635953</v>
+        <v>6635976</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,6 +1481,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1485,10 +1500,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117939212</v>
+        <v>117941588</v>
       </c>
       <c r="B9" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,7 +1535,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1539,10 +1554,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>692482</v>
+        <v>692530</v>
       </c>
       <c r="R9" t="n">
-        <v>6635862</v>
+        <v>6635831</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1601,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117939096</v>
+        <v>117938588</v>
       </c>
       <c r="B10" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,7 +1651,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1644,16 +1659,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>692535</v>
+        <v>692521</v>
       </c>
       <c r="R10" t="n">
-        <v>6635930</v>
+        <v>6635907</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,19 +1703,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,22 +1720,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117939430</v>
+        <v>117937309</v>
       </c>
       <c r="B11" t="n">
-        <v>90517</v>
+        <v>97838</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,38 +1744,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>692467</v>
+        <v>692610</v>
       </c>
       <c r="R11" t="n">
-        <v>6635836</v>
+        <v>6635980</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,9 +1819,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,10 +1858,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117938174</v>
+        <v>117938431</v>
       </c>
       <c r="B12" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,7 +1893,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1867,24 +1901,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>692551</v>
+        <v>692527</v>
       </c>
       <c r="R12" t="n">
-        <v>6635923</v>
+        <v>6635949</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1911,9 +1940,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,22 +1967,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117942112</v>
+        <v>117942210</v>
       </c>
       <c r="B13" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,7 +2014,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1983,16 +2022,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>692538</v>
+        <v>692602</v>
       </c>
       <c r="R13" t="n">
-        <v>6635877</v>
+        <v>6635953</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,24 +2066,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,22 +2083,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117938975</v>
+        <v>117937256</v>
       </c>
       <c r="B14" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2116,14 +2145,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>692514</v>
+        <v>692608</v>
       </c>
       <c r="R14" t="n">
-        <v>6635894</v>
+        <v>6635981</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2182,10 +2211,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117937314</v>
+        <v>117941342</v>
       </c>
       <c r="B15" t="n">
-        <v>97836</v>
+        <v>5166</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,50 +2223,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>692583</v>
+        <v>692449</v>
       </c>
       <c r="R15" t="n">
-        <v>6635986</v>
+        <v>6635786</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2266,7 +2286,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2296,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,10 +2323,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117939347</v>
+        <v>117941471</v>
       </c>
       <c r="B16" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2338,7 +2358,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2352,10 +2372,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>692449</v>
+        <v>692463</v>
       </c>
       <c r="R16" t="n">
-        <v>6635952</v>
+        <v>6635816</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2387,7 +2407,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2397,12 +2417,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Två med knoppiga blomstänglar</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2429,10 +2444,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117940804</v>
+        <v>117942036</v>
       </c>
       <c r="B17" t="n">
-        <v>5186</v>
+        <v>97838</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2441,47 +2456,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>692436</v>
+        <v>692568</v>
       </c>
       <c r="R17" t="n">
-        <v>6635782</v>
+        <v>6635907</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2522,7 +2542,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2541,10 +2560,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117938588</v>
+        <v>117937630</v>
       </c>
       <c r="B18" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2576,7 +2595,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2586,19 +2605,19 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Sjöstugan (Sjöstugan), Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>692521</v>
+        <v>692596</v>
       </c>
       <c r="R18" t="n">
-        <v>6635907</v>
+        <v>6635973</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2657,10 +2676,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117941687</v>
+        <v>117941737</v>
       </c>
       <c r="B19" t="n">
-        <v>97836</v>
+        <v>100099</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2669,52 +2688,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>692553</v>
+        <v>692563</v>
       </c>
       <c r="R19" t="n">
-        <v>6635890</v>
+        <v>6635887</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2773,10 +2778,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117937690</v>
+        <v>117942312</v>
       </c>
       <c r="B20" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2808,7 +2813,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2816,19 +2821,24 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>692585</v>
+        <v>692611</v>
       </c>
       <c r="R20" t="n">
-        <v>6635997</v>
+        <v>6635972</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2855,19 +2865,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2882,22 +2882,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117937555</v>
+        <v>117937381</v>
       </c>
       <c r="B21" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2937,24 +2937,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>692599</v>
+        <v>692597</v>
       </c>
       <c r="R21" t="n">
-        <v>6635973</v>
+        <v>6635979</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2981,9 +2976,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2998,22 +3003,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117938026</v>
+        <v>117937927</v>
       </c>
       <c r="B22" t="n">
-        <v>57303</v>
+        <v>97838</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3022,31 +3027,40 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3055,10 +3069,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>692573</v>
+        <v>692577</v>
       </c>
       <c r="R22" t="n">
-        <v>6635947</v>
+        <v>6635977</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3117,10 +3131,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117937256</v>
+        <v>117937975</v>
       </c>
       <c r="B23" t="n">
-        <v>97836</v>
+        <v>57304</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3129,52 +3143,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>692608</v>
+        <v>692575</v>
       </c>
       <c r="R23" t="n">
-        <v>6635981</v>
+        <v>6635954</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3233,10 +3238,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117937556</v>
+        <v>117941899</v>
       </c>
       <c r="B24" t="n">
-        <v>97836</v>
+        <v>90501</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3245,50 +3250,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>692602</v>
+        <v>692580</v>
       </c>
       <c r="R24" t="n">
-        <v>6635995</v>
+        <v>6635891</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3315,24 +3311,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3347,22 +3328,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117942312</v>
+        <v>117938174</v>
       </c>
       <c r="B25" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3394,7 +3375,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3413,10 +3394,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>692611</v>
+        <v>692551</v>
       </c>
       <c r="R25" t="n">
-        <v>6635972</v>
+        <v>6635923</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3475,10 +3456,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117939029</v>
+        <v>117941966</v>
       </c>
       <c r="B26" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3510,7 +3491,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3529,10 +3510,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>692506</v>
+        <v>692578</v>
       </c>
       <c r="R26" t="n">
-        <v>6635887</v>
+        <v>6635898</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3591,10 +3572,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117937381</v>
+        <v>117939062</v>
       </c>
       <c r="B27" t="n">
-        <v>97836</v>
+        <v>5166</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3603,50 +3584,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>692597</v>
+        <v>692498</v>
       </c>
       <c r="R27" t="n">
-        <v>6635979</v>
+        <v>6635884</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3673,19 +3650,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3700,22 +3667,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117937927</v>
+        <v>117939430</v>
       </c>
       <c r="B28" t="n">
-        <v>97836</v>
+        <v>90519</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3724,52 +3691,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>692577</v>
+        <v>692467</v>
       </c>
       <c r="R28" t="n">
-        <v>6635977</v>
+        <v>6635836</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3828,10 +3781,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117938005</v>
+        <v>117938026</v>
       </c>
       <c r="B29" t="n">
-        <v>57768</v>
+        <v>57304</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3844,34 +3797,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>692578</v>
+        <v>692573</v>
       </c>
       <c r="R29" t="n">
-        <v>6635954</v>
+        <v>6635947</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3930,10 +3888,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117938213</v>
+        <v>117938005</v>
       </c>
       <c r="B30" t="n">
-        <v>97836</v>
+        <v>57769</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3942,50 +3900,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103018</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>692555</v>
+        <v>692578</v>
       </c>
       <c r="R30" t="n">
-        <v>6635951</v>
+        <v>6635954</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4012,24 +3961,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>4 med knoppig blomstängel tv</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4044,22 +3978,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117941641</v>
+        <v>117937784</v>
       </c>
       <c r="B31" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4091,7 +4025,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4101,22 +4035,22 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>692543</v>
+        <v>692568</v>
       </c>
       <c r="R31" t="n">
-        <v>6635857</v>
+        <v>6635991</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4143,9 +4077,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4160,22 +4109,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117941966</v>
+        <v>117937494</v>
       </c>
       <c r="B32" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4207,7 +4156,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4222,14 +4171,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>692578</v>
+        <v>692606</v>
       </c>
       <c r="R32" t="n">
-        <v>6635898</v>
+        <v>6635979</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4259,9 +4208,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4288,10 +4247,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117937975</v>
+        <v>117940890</v>
       </c>
       <c r="B33" t="n">
-        <v>57303</v>
+        <v>97838</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4300,31 +4259,40 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4333,10 +4301,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>692575</v>
+        <v>692459</v>
       </c>
       <c r="R33" t="n">
-        <v>6635954</v>
+        <v>6635787</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4395,10 +4363,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117939282</v>
+        <v>117941678</v>
       </c>
       <c r="B34" t="n">
-        <v>57303</v>
+        <v>97838</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4407,43 +4375,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>692487</v>
+        <v>692496</v>
       </c>
       <c r="R34" t="n">
-        <v>6635864</v>
+        <v>6635822</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4473,9 +4445,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4490,22 +4477,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117939062</v>
+        <v>117938981</v>
       </c>
       <c r="B35" t="n">
-        <v>5166</v>
+        <v>97838</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4514,43 +4501,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>692498</v>
+        <v>692535</v>
       </c>
       <c r="R35" t="n">
-        <v>6635884</v>
+        <v>6635930</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4580,9 +4571,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4597,22 +4598,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117941342</v>
+        <v>117939029</v>
       </c>
       <c r="B36" t="n">
-        <v>5166</v>
+        <v>97838</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4621,38 +4622,52 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>692449</v>
+        <v>692506</v>
       </c>
       <c r="R36" t="n">
-        <v>6635786</v>
+        <v>6635887</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4682,19 +4697,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4709,22 +4714,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117941471</v>
+        <v>117939581</v>
       </c>
       <c r="B37" t="n">
-        <v>97836</v>
+        <v>57304</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4733,47 +4738,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>692463</v>
+        <v>692448</v>
       </c>
       <c r="R37" t="n">
-        <v>6635816</v>
+        <v>6635840</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4803,19 +4804,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4830,22 +4821,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117937784</v>
+        <v>117940793</v>
       </c>
       <c r="B38" t="n">
-        <v>97836</v>
+        <v>5166</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4854,55 +4845,50 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>692568</v>
+        <v>692434</v>
       </c>
       <c r="R38" t="n">
-        <v>6635991</v>
+        <v>6635779</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4929,54 +4915,40 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117941545</v>
+        <v>117942075</v>
       </c>
       <c r="B39" t="n">
-        <v>57303</v>
+        <v>97838</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4985,31 +4957,40 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5018,10 +4999,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>692519</v>
+        <v>692570</v>
       </c>
       <c r="R39" t="n">
-        <v>6635833</v>
+        <v>6635906</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5080,10 +5061,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117937862</v>
+        <v>117937995</v>
       </c>
       <c r="B40" t="n">
-        <v>5186</v>
+        <v>97838</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5092,50 +5073,50 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>692594</v>
+        <v>692584</v>
       </c>
       <c r="R40" t="n">
-        <v>6635976</v>
+        <v>6635955</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5162,40 +5143,49 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117939382</v>
+        <v>117938225</v>
       </c>
       <c r="B41" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5227,7 +5217,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5246,10 +5236,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>692463</v>
+        <v>692543</v>
       </c>
       <c r="R41" t="n">
-        <v>6635839</v>
+        <v>6635916</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5308,10 +5298,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117937630</v>
+        <v>117937690</v>
       </c>
       <c r="B42" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5343,7 +5333,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5351,24 +5341,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sjöstugan (Sjöstugan), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>692596</v>
+        <v>692585</v>
       </c>
       <c r="R42" t="n">
-        <v>6635973</v>
+        <v>6635997</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5395,9 +5380,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5412,22 +5407,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117942036</v>
+        <v>117937628</v>
       </c>
       <c r="B43" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5459,7 +5454,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5467,24 +5462,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>692568</v>
+        <v>692583</v>
       </c>
       <c r="R43" t="n">
-        <v>6635907</v>
+        <v>6635987</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5511,9 +5501,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5528,22 +5533,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117941588</v>
+        <v>117938311</v>
       </c>
       <c r="B44" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5575,7 +5580,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5583,24 +5588,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>692530</v>
+        <v>692539</v>
       </c>
       <c r="R44" t="n">
-        <v>6635831</v>
+        <v>6635922</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5627,9 +5627,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5644,22 +5659,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117937494</v>
+        <v>117937555</v>
       </c>
       <c r="B45" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5691,7 +5706,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5710,10 +5725,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>692606</v>
+        <v>692599</v>
       </c>
       <c r="R45" t="n">
-        <v>6635979</v>
+        <v>6635973</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5743,19 +5758,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:42</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5782,10 +5787,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117942075</v>
+        <v>117941865</v>
       </c>
       <c r="B46" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5817,7 +5822,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5825,21 +5830,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>692570</v>
+        <v>692513</v>
       </c>
       <c r="R46" t="n">
-        <v>6635906</v>
+        <v>6635854</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5869,9 +5869,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5886,22 +5901,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117941865</v>
+        <v>117940804</v>
       </c>
       <c r="B47" t="n">
-        <v>97836</v>
+        <v>5186</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5910,47 +5925,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>692513</v>
+        <v>692436</v>
       </c>
       <c r="R47" t="n">
-        <v>6635854</v>
+        <v>6635782</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5980,54 +5995,40 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117937214</v>
+        <v>117939070</v>
       </c>
       <c r="B48" t="n">
-        <v>97836</v>
+        <v>5186</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6036,52 +6037,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön (Sjöstugan), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>692607</v>
+        <v>692498</v>
       </c>
       <c r="R48" t="n">
-        <v>6635979</v>
+        <v>6635884</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6140,10 +6132,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117938311</v>
+        <v>117941641</v>
       </c>
       <c r="B49" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6175,7 +6167,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6183,19 +6175,24 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>692539</v>
+        <v>692543</v>
       </c>
       <c r="R49" t="n">
-        <v>6635922</v>
+        <v>6635857</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6222,24 +6219,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6254,22 +6236,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117937309</v>
+        <v>117939275</v>
       </c>
       <c r="B50" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6301,7 +6283,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6309,21 +6291,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>692610</v>
+        <v>692449</v>
       </c>
       <c r="R50" t="n">
-        <v>6635980</v>
+        <v>6635952</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6355,7 +6332,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6365,7 +6342,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6380,22 +6357,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117938132</v>
+        <v>117938213</v>
       </c>
       <c r="B51" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6427,7 +6404,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6435,24 +6412,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>692562</v>
+        <v>692555</v>
       </c>
       <c r="R51" t="n">
-        <v>6635932</v>
+        <v>6635951</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6479,9 +6451,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>4 med knoppig blomstängel tv</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6496,22 +6483,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117939088</v>
+        <v>117942921</v>
       </c>
       <c r="B52" t="n">
-        <v>97836</v>
+        <v>5166</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6520,55 +6507,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>692498</v>
+        <v>692583</v>
       </c>
       <c r="R52" t="n">
-        <v>6635884</v>
+        <v>6635986</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6595,9 +6568,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6612,22 +6595,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117937938</v>
+        <v>117939212</v>
       </c>
       <c r="B53" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6659,7 +6642,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6667,19 +6650,24 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>692549</v>
+        <v>692482</v>
       </c>
       <c r="R53" t="n">
-        <v>6635965</v>
+        <v>6635862</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6706,19 +6694,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6733,22 +6711,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117938431</v>
+        <v>117938795</v>
       </c>
       <c r="B54" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6780,7 +6758,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6788,19 +6766,24 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>692527</v>
+        <v>692508</v>
       </c>
       <c r="R54" t="n">
-        <v>6635949</v>
+        <v>6635905</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6827,19 +6810,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6854,22 +6827,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117941596</v>
+        <v>117937757</v>
       </c>
       <c r="B55" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6901,7 +6874,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6909,16 +6882,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>692474</v>
+        <v>692596</v>
       </c>
       <c r="R55" t="n">
-        <v>6635824</v>
+        <v>6635955</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6948,19 +6926,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6975,22 +6943,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117942921</v>
+        <v>117938661</v>
       </c>
       <c r="B56" t="n">
-        <v>5166</v>
+        <v>97838</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6999,41 +6967,55 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön, Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>692583</v>
+        <v>692521</v>
       </c>
       <c r="R56" t="n">
-        <v>6635986</v>
+        <v>6635910</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7060,19 +7042,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:13</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7087,22 +7059,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117940793</v>
+        <v>117939282</v>
       </c>
       <c r="B57" t="n">
-        <v>5166</v>
+        <v>57304</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7111,47 +7083,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>692434</v>
+        <v>692487</v>
       </c>
       <c r="R57" t="n">
-        <v>6635779</v>
+        <v>6635864</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7192,7 +7160,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7211,10 +7178,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117939646</v>
+        <v>117942112</v>
       </c>
       <c r="B58" t="n">
-        <v>5186</v>
+        <v>97838</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7223,47 +7190,47 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>692415</v>
+        <v>692538</v>
       </c>
       <c r="R58" t="n">
-        <v>6635846</v>
+        <v>6635877</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7293,40 +7260,54 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>En knoppig blomstängel</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117939581</v>
+        <v>117938975</v>
       </c>
       <c r="B59" t="n">
-        <v>57303</v>
+        <v>97838</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7335,31 +7316,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7368,10 +7358,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>692448</v>
+        <v>692514</v>
       </c>
       <c r="R59" t="n">
-        <v>6635840</v>
+        <v>6635894</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7430,10 +7420,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117941484</v>
+        <v>117941545</v>
       </c>
       <c r="B60" t="n">
-        <v>90517</v>
+        <v>57304</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7446,34 +7436,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>692520</v>
+        <v>692519</v>
       </c>
       <c r="R60" t="n">
-        <v>6635829</v>
+        <v>6635833</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7532,10 +7527,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117940890</v>
+        <v>117938078</v>
       </c>
       <c r="B61" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7567,7 +7562,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7586,10 +7581,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>692459</v>
+        <v>692569</v>
       </c>
       <c r="R61" t="n">
-        <v>6635787</v>
+        <v>6635939</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7648,10 +7643,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117941737</v>
+        <v>117938132</v>
       </c>
       <c r="B62" t="n">
-        <v>100097</v>
+        <v>97838</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7660,38 +7655,52 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>692563</v>
+        <v>692562</v>
       </c>
       <c r="R62" t="n">
-        <v>6635887</v>
+        <v>6635932</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7750,10 +7759,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117938078</v>
+        <v>117937992</v>
       </c>
       <c r="B63" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7785,7 +7794,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7804,10 +7813,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>692569</v>
+        <v>692573</v>
       </c>
       <c r="R63" t="n">
-        <v>6635939</v>
+        <v>6635954</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7866,10 +7875,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117937995</v>
+        <v>117939646</v>
       </c>
       <c r="B64" t="n">
-        <v>97836</v>
+        <v>5186</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7878,50 +7887,50 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>692584</v>
+        <v>692415</v>
       </c>
       <c r="R64" t="n">
-        <v>6635955</v>
+        <v>6635846</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7948,49 +7957,40 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117938661</v>
+        <v>117939187</v>
       </c>
       <c r="B65" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8041,10 +8041,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>692521</v>
+        <v>692474</v>
       </c>
       <c r="R65" t="n">
-        <v>6635910</v>
+        <v>6635872</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8103,10 +8103,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117941678</v>
+        <v>117939382</v>
       </c>
       <c r="B66" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8146,16 +8146,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>692496</v>
+        <v>692463</v>
       </c>
       <c r="R66" t="n">
-        <v>6635822</v>
+        <v>6635839</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8185,24 +8190,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8217,22 +8207,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117937628</v>
+        <v>117941596</v>
       </c>
       <c r="B67" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8264,7 +8254,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8278,13 +8268,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>692583</v>
+        <v>692474</v>
       </c>
       <c r="R67" t="n">
-        <v>6635987</v>
+        <v>6635824</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8313,7 +8303,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8323,12 +8313,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8355,10 +8340,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117939187</v>
+        <v>117941484</v>
       </c>
       <c r="B68" t="n">
-        <v>97836</v>
+        <v>90519</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8367,52 +8352,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>692474</v>
+        <v>692520</v>
       </c>
       <c r="R68" t="n">
-        <v>6635872</v>
+        <v>6635829</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8471,10 +8442,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117938225</v>
+        <v>117938933</v>
       </c>
       <c r="B69" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8506,7 +8477,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8525,10 +8496,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>692543</v>
+        <v>692516</v>
       </c>
       <c r="R69" t="n">
-        <v>6635916</v>
+        <v>6635890</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8587,10 +8558,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117937757</v>
+        <v>117937556</v>
       </c>
       <c r="B70" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8622,7 +8593,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8630,24 +8601,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>692596</v>
+        <v>692602</v>
       </c>
       <c r="R70" t="n">
-        <v>6635955</v>
+        <v>6635995</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8674,9 +8640,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8691,22 +8672,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117939070</v>
+        <v>117937214</v>
       </c>
       <c r="B71" t="n">
-        <v>5186</v>
+        <v>97838</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8715,43 +8696,52 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön (Sjöstugan), Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>692498</v>
+        <v>692607</v>
       </c>
       <c r="R71" t="n">
-        <v>6635884</v>
+        <v>6635979</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8810,10 +8800,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117941752</v>
+        <v>117939183</v>
       </c>
       <c r="B72" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8845,7 +8835,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8853,21 +8843,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>692560</v>
+        <v>692452</v>
       </c>
       <c r="R72" t="n">
-        <v>6635889</v>
+        <v>6635944</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8897,9 +8882,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8914,12 +8909,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8929,7 +8924,7 @@
         <v>117985443</v>
       </c>
       <c r="B73" t="n">
-        <v>90513</v>
+        <v>90515</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>

--- a/artfynd/A 20722-2024 artfynd.xlsx
+++ b/artfynd/A 20722-2024 artfynd.xlsx
@@ -2095,10 +2095,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117937256</v>
+        <v>117941342</v>
       </c>
       <c r="B14" t="n">
-        <v>97838</v>
+        <v>5166</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2107,52 +2107,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>692608</v>
+        <v>692449</v>
       </c>
       <c r="R14" t="n">
-        <v>6635981</v>
+        <v>6635786</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2182,9 +2168,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2199,22 +2195,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117941342</v>
+        <v>117937256</v>
       </c>
       <c r="B15" t="n">
-        <v>5166</v>
+        <v>97838</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2223,38 +2219,52 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>692449</v>
+        <v>692608</v>
       </c>
       <c r="R15" t="n">
-        <v>6635786</v>
+        <v>6635981</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2284,19 +2294,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2311,12 +2311,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117939430</v>
+        <v>117937784</v>
       </c>
       <c r="B28" t="n">
-        <v>90519</v>
+        <v>97838</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3691,41 +3691,55 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>692467</v>
+        <v>692568</v>
       </c>
       <c r="R28" t="n">
-        <v>6635836</v>
+        <v>6635991</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3752,9 +3766,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3769,22 +3798,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117938026</v>
+        <v>117939430</v>
       </c>
       <c r="B29" t="n">
-        <v>57304</v>
+        <v>90519</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3797,39 +3826,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>692573</v>
+        <v>692467</v>
       </c>
       <c r="R29" t="n">
-        <v>6635947</v>
+        <v>6635836</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3888,10 +3912,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117938005</v>
+        <v>117938026</v>
       </c>
       <c r="B30" t="n">
-        <v>57769</v>
+        <v>57304</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3904,34 +3928,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>692578</v>
+        <v>692573</v>
       </c>
       <c r="R30" t="n">
-        <v>6635954</v>
+        <v>6635947</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3990,10 +4019,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117937784</v>
+        <v>117938005</v>
       </c>
       <c r="B31" t="n">
-        <v>97838</v>
+        <v>57769</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4002,55 +4031,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>103018</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>692568</v>
+        <v>692578</v>
       </c>
       <c r="R31" t="n">
-        <v>6635991</v>
+        <v>6635954</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4077,24 +4092,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4109,12 +4109,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -6369,10 +6369,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117938213</v>
+        <v>117942921</v>
       </c>
       <c r="B51" t="n">
-        <v>97838</v>
+        <v>5166</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6381,50 +6381,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>692555</v>
+        <v>692583</v>
       </c>
       <c r="R51" t="n">
-        <v>6635951</v>
+        <v>6635986</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6453,7 +6444,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6463,12 +6454,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>4 med knoppig blomstängel tv</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6495,10 +6481,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117942921</v>
+        <v>117938213</v>
       </c>
       <c r="B52" t="n">
-        <v>5166</v>
+        <v>97838</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6507,41 +6493,50 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön, Upl</t>
+          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>692583</v>
+        <v>692555</v>
       </c>
       <c r="R52" t="n">
-        <v>6635986</v>
+        <v>6635951</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6570,7 +6565,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6580,7 +6575,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>4 med knoppig blomstängel tv</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 20722-2024 artfynd.xlsx
+++ b/artfynd/A 20722-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68600728</v>
+        <v>117941899</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,36 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norr om Pottåkersjön, Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>692323.1173352157</v>
+        <v>692580</v>
       </c>
       <c r="R2" t="n">
-        <v>6635903.928606862</v>
+        <v>6635891</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -747,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-04-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-04-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På flera gamla granar tillsammans med andra hänglavar.</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,31 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hilde Nystad</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hilde Nystad, Lukas Scholz, Per Bengtson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Skogsgruppen, RNF</t>
-        </is>
-      </c>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117937690</v>
+        <v>117985443</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,46 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692585</v>
+        <v>692541</v>
       </c>
       <c r="R3" t="n">
-        <v>6635997</v>
+        <v>6635891</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +842,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +852,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,27 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117937381</v>
+        <v>68600728</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,46 +890,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Norr om Pottåkersjön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>692597</v>
+        <v>692323</v>
       </c>
       <c r="R4" t="n">
-        <v>6635979</v>
+        <v>6635904</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,22 +946,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2017-04-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2017-04-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På flera gamla granar tillsammans med andra hänglavar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,71 +971,61 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Hilde Nystad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Hilde Nystad, Lukas Scholz, Per Bengtson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skogsgruppen, RNF</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117941596</v>
+        <v>117941122</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>692474</v>
+        <v>692428</v>
       </c>
       <c r="R5" t="n">
-        <v>6635824</v>
+        <v>6635720</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,19 +1055,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,62 +1072,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117941899</v>
+        <v>117937975</v>
       </c>
       <c r="B6" t="n">
-        <v>90504</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>692580</v>
+        <v>692575</v>
       </c>
       <c r="R6" t="n">
-        <v>6635891</v>
+        <v>6635954</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1263,64 +1186,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117938933</v>
+        <v>117938026</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>692516</v>
+        <v>692573</v>
       </c>
       <c r="R7" t="n">
-        <v>6635890</v>
+        <v>6635947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,62 +1288,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117943920</v>
+        <v>117939282</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön, Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>692583</v>
+        <v>692487</v>
       </c>
       <c r="R8" t="n">
-        <v>6635986</v>
+        <v>6635864</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,24 +1361,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,76 +1378,62 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117938588</v>
+        <v>117939581</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>692521</v>
+        <v>692448</v>
       </c>
       <c r="R9" t="n">
-        <v>6635907</v>
+        <v>6635840</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1621,64 +1492,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117942075</v>
+        <v>117941545</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>692570</v>
+        <v>692519</v>
       </c>
       <c r="R10" t="n">
-        <v>6635906</v>
+        <v>6635833</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1737,64 +1594,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117938174</v>
+        <v>117939062</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>692551</v>
+        <v>692498</v>
       </c>
       <c r="R11" t="n">
-        <v>6635923</v>
+        <v>6635884</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1853,55 +1696,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117939282</v>
+        <v>117940793</v>
       </c>
       <c r="B12" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>692487</v>
+        <v>692434</v>
       </c>
       <c r="R12" t="n">
-        <v>6635864</v>
+        <v>6635779</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1942,6 +1784,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1960,15 +1803,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117939646</v>
+        <v>117941342</v>
       </c>
       <c r="B13" t="n">
-        <v>5186</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1976,43 +1814,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>692415</v>
+        <v>692449</v>
       </c>
       <c r="R13" t="n">
-        <v>6635846</v>
+        <v>6635786</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2042,97 +1871,87 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117937494</v>
+        <v>117942921</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>692606</v>
+        <v>692583</v>
       </c>
       <c r="R14" t="n">
-        <v>6635979</v>
+        <v>6635986</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2161,7 +1980,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2171,7 +1990,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2186,76 +2005,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117942312</v>
+        <v>117938005</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103018</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>692611</v>
+        <v>692578</v>
       </c>
       <c r="R15" t="n">
-        <v>6635972</v>
+        <v>6635954</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2314,64 +2114,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117938795</v>
+        <v>117937862</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Sjöstugan, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>692508</v>
+        <v>692594</v>
       </c>
       <c r="R16" t="n">
-        <v>6635905</v>
+        <v>6635976</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2412,6 +2202,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2430,64 +2221,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117937927</v>
+        <v>117939070</v>
       </c>
       <c r="B17" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>692577</v>
+        <v>692498</v>
       </c>
       <c r="R17" t="n">
-        <v>6635977</v>
+        <v>6635884</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2546,59 +2323,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117941471</v>
+        <v>117939646</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>692463</v>
+        <v>692415</v>
       </c>
       <c r="R18" t="n">
-        <v>6635816</v>
+        <v>6635846</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2628,103 +2400,84 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117939212</v>
+        <v>117940804</v>
       </c>
       <c r="B19" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>692482</v>
+        <v>692436</v>
       </c>
       <c r="R19" t="n">
-        <v>6635862</v>
+        <v>6635782</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2765,6 +2518,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2783,15 +2537,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117942036</v>
+        <v>117937214</v>
       </c>
       <c r="B20" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2818,7 +2567,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2833,14 +2582,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön, Sjöstugan, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>692568</v>
+        <v>692607</v>
       </c>
       <c r="R20" t="n">
-        <v>6635907</v>
+        <v>6635979</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2899,15 +2648,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117937556</v>
+        <v>117937256</v>
       </c>
       <c r="B21" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2934,7 +2678,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2942,19 +2686,24 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Sjöstugan, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>692602</v>
+        <v>692608</v>
       </c>
       <c r="R21" t="n">
-        <v>6635995</v>
+        <v>6635981</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2981,24 +2730,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3013,27 +2747,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117941641</v>
+        <v>117937309</v>
       </c>
       <c r="B22" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3060,7 +2789,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3070,19 +2799,19 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Sjöstugan, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>692543</v>
+        <v>692610</v>
       </c>
       <c r="R22" t="n">
-        <v>6635857</v>
+        <v>6635980</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3112,9 +2841,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3141,15 +2880,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117938431</v>
+        <v>117937314</v>
       </c>
       <c r="B23" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3176,7 +2910,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3186,17 +2920,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>692527</v>
+        <v>692583</v>
       </c>
       <c r="R23" t="n">
-        <v>6635949</v>
+        <v>6635986</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3225,7 +2959,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3235,7 +2969,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3262,58 +2996,57 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117941545</v>
+        <v>117937381</v>
       </c>
       <c r="B24" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>692519</v>
+        <v>692597</v>
       </c>
       <c r="R24" t="n">
-        <v>6635833</v>
+        <v>6635979</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3340,9 +3073,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3357,27 +3100,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117939347</v>
+        <v>117937494</v>
       </c>
       <c r="B25" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3404,7 +3142,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3412,16 +3150,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Sjöstugan, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>692449</v>
+        <v>692606</v>
       </c>
       <c r="R25" t="n">
-        <v>6635952</v>
+        <v>6635979</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3453,7 +3196,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3463,12 +3206,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Två med knoppiga blomstänglar</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3483,27 +3221,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117940890</v>
+        <v>117937555</v>
       </c>
       <c r="B26" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3530,7 +3263,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3545,14 +3278,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Sjöstugan, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>692459</v>
+        <v>692599</v>
       </c>
       <c r="R26" t="n">
-        <v>6635787</v>
+        <v>6635973</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3611,15 +3344,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117941966</v>
+        <v>117937556</v>
       </c>
       <c r="B27" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3646,7 +3374,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3654,24 +3382,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>692578</v>
+        <v>692602</v>
       </c>
       <c r="R27" t="n">
-        <v>6635898</v>
+        <v>6635995</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3698,9 +3421,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3715,67 +3453,71 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117939062</v>
+        <v>117937630</v>
       </c>
       <c r="B28" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Sjöstugan, Sjöstugan, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>692498</v>
+        <v>692596</v>
       </c>
       <c r="R28" t="n">
-        <v>6635884</v>
+        <v>6635973</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3834,15 +3576,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117942112</v>
+        <v>117937690</v>
       </c>
       <c r="B29" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3869,7 +3606,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3879,17 +3616,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>692538</v>
+        <v>692585</v>
       </c>
       <c r="R29" t="n">
-        <v>6635877</v>
+        <v>6635997</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3918,7 +3655,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3928,12 +3665,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:44</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3960,15 +3692,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117941588</v>
+        <v>117937757</v>
       </c>
       <c r="B30" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3995,7 +3722,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4005,19 +3732,19 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Sjöstugan, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>692530</v>
+        <v>692596</v>
       </c>
       <c r="R30" t="n">
-        <v>6635831</v>
+        <v>6635955</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4076,15 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117937628</v>
+        <v>117937784</v>
       </c>
       <c r="B31" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4111,7 +3833,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4119,16 +3841,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>692583</v>
+        <v>692568</v>
       </c>
       <c r="R31" t="n">
-        <v>6635987</v>
+        <v>6635991</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4160,7 +3887,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4170,7 +3897,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4202,15 +3929,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117937214</v>
+        <v>117937927</v>
       </c>
       <c r="B32" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4237,7 +3959,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4247,19 +3969,19 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön (Sjöstugan), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>692607</v>
+        <v>692577</v>
       </c>
       <c r="R32" t="n">
-        <v>6635979</v>
+        <v>6635977</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4318,15 +4040,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117937995</v>
+        <v>117937938</v>
       </c>
       <c r="B33" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4353,7 +4070,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4363,14 +4080,14 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>692584</v>
+        <v>692549</v>
       </c>
       <c r="R33" t="n">
-        <v>6635955</v>
+        <v>6635965</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4402,7 +4119,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4412,7 +4129,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4439,15 +4156,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117939088</v>
+        <v>117937992</v>
       </c>
       <c r="B34" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4474,7 +4186,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4489,14 +4201,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>692498</v>
+        <v>692573</v>
       </c>
       <c r="R34" t="n">
-        <v>6635884</v>
+        <v>6635954</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4555,15 +4267,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117941865</v>
+        <v>117937995</v>
       </c>
       <c r="B35" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4590,7 +4297,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4600,17 +4307,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>692513</v>
+        <v>692584</v>
       </c>
       <c r="R35" t="n">
-        <v>6635854</v>
+        <v>6635955</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4639,7 +4346,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4649,12 +4356,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4681,15 +4383,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117938661</v>
+        <v>117938078</v>
       </c>
       <c r="B36" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4716,7 +4413,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4731,14 +4428,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>692521</v>
+        <v>692569</v>
       </c>
       <c r="R36" t="n">
-        <v>6635910</v>
+        <v>6635939</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4797,15 +4494,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117938975</v>
+        <v>117938132</v>
       </c>
       <c r="B37" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4832,7 +4524,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4847,14 +4539,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>692514</v>
+        <v>692562</v>
       </c>
       <c r="R37" t="n">
-        <v>6635894</v>
+        <v>6635932</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4913,55 +4605,59 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117938026</v>
+        <v>117938174</v>
       </c>
       <c r="B38" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>692573</v>
+        <v>692551</v>
       </c>
       <c r="R38" t="n">
-        <v>6635947</v>
+        <v>6635923</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5020,58 +4716,57 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117939581</v>
+        <v>117938213</v>
       </c>
       <c r="B39" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>692448</v>
+        <v>692555</v>
       </c>
       <c r="R39" t="n">
-        <v>6635840</v>
+        <v>6635951</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5098,9 +4793,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>4 med knoppig blomstängel tv</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5115,27 +4825,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117937309</v>
+        <v>117938225</v>
       </c>
       <c r="B40" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5162,7 +4867,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5172,19 +4877,19 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>692610</v>
+        <v>692543</v>
       </c>
       <c r="R40" t="n">
-        <v>6635980</v>
+        <v>6635916</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5214,19 +4919,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5253,15 +4948,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117939029</v>
+        <v>117938311</v>
       </c>
       <c r="B41" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5288,7 +4978,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5296,24 +4986,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>692506</v>
+        <v>692539</v>
       </c>
       <c r="R41" t="n">
-        <v>6635887</v>
+        <v>6635922</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5340,9 +5025,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5357,27 +5057,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117939187</v>
+        <v>117938431</v>
       </c>
       <c r="B42" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5404,7 +5099,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5412,24 +5107,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>692474</v>
+        <v>692527</v>
       </c>
       <c r="R42" t="n">
-        <v>6635872</v>
+        <v>6635949</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5456,9 +5146,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5473,27 +5173,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117937630</v>
+        <v>117938580</v>
       </c>
       <c r="B43" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5520,7 +5215,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5528,21 +5223,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sjöstugan (Sjöstugan), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>692596</v>
+        <v>692535</v>
       </c>
       <c r="R43" t="n">
-        <v>6635973</v>
+        <v>6635930</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5572,9 +5262,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5589,27 +5289,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117938213</v>
+        <v>117938588</v>
       </c>
       <c r="B44" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5636,7 +5331,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5644,19 +5339,24 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>692555</v>
+        <v>692521</v>
       </c>
       <c r="R44" t="n">
-        <v>6635951</v>
+        <v>6635907</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5683,24 +5383,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>4 med knoppig blomstängel tv</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5715,27 +5400,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117941678</v>
+        <v>117938661</v>
       </c>
       <c r="B45" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5762,7 +5442,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5770,16 +5450,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>692496</v>
+        <v>692521</v>
       </c>
       <c r="R45" t="n">
-        <v>6635822</v>
+        <v>6635910</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5809,24 +5494,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5841,27 +5511,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117937555</v>
+        <v>117938795</v>
       </c>
       <c r="B46" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5888,7 +5553,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5903,14 +5568,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>692599</v>
+        <v>692508</v>
       </c>
       <c r="R46" t="n">
-        <v>6635973</v>
+        <v>6635905</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5969,15 +5634,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117939382</v>
+        <v>117938933</v>
       </c>
       <c r="B47" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6004,7 +5664,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6019,14 +5679,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>692463</v>
+        <v>692516</v>
       </c>
       <c r="R47" t="n">
-        <v>6635839</v>
+        <v>6635890</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6085,15 +5745,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117937992</v>
+        <v>117938975</v>
       </c>
       <c r="B48" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6120,7 +5775,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6135,14 +5790,14 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>692573</v>
+        <v>692514</v>
       </c>
       <c r="R48" t="n">
-        <v>6635954</v>
+        <v>6635894</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6201,55 +5856,59 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117937975</v>
+        <v>117939029</v>
       </c>
       <c r="B49" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>692575</v>
+        <v>692506</v>
       </c>
       <c r="R49" t="n">
-        <v>6635954</v>
+        <v>6635887</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6308,15 +5967,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117941687</v>
+        <v>117939088</v>
       </c>
       <c r="B50" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6343,7 +5997,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6358,14 +6012,14 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>692553</v>
+        <v>692498</v>
       </c>
       <c r="R50" t="n">
-        <v>6635890</v>
+        <v>6635884</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6427,12 +6081,7 @@
         <v>117939183</v>
       </c>
       <c r="B51" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6469,7 +6118,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
@@ -6545,15 +6194,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117938225</v>
+        <v>117939187</v>
       </c>
       <c r="B52" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6580,7 +6224,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6595,14 +6239,14 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>692543</v>
+        <v>692474</v>
       </c>
       <c r="R52" t="n">
-        <v>6635916</v>
+        <v>6635872</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6661,15 +6305,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117937784</v>
+        <v>117939212</v>
       </c>
       <c r="B53" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6696,7 +6335,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6706,22 +6345,22 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>692568</v>
+        <v>692482</v>
       </c>
       <c r="R53" t="n">
-        <v>6635991</v>
+        <v>6635862</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6748,24 +6387,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6780,62 +6404,66 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117939430</v>
+        <v>117939275</v>
       </c>
       <c r="B54" t="n">
-        <v>90522</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>692467</v>
+        <v>692449</v>
       </c>
       <c r="R54" t="n">
-        <v>6635836</v>
+        <v>6635952</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6865,9 +6493,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6882,27 +6520,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117938580</v>
+        <v>117939382</v>
       </c>
       <c r="B55" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6929,7 +6562,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6937,16 +6570,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>692535</v>
+        <v>692463</v>
       </c>
       <c r="R55" t="n">
-        <v>6635930</v>
+        <v>6635839</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6976,19 +6614,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7003,27 +6631,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117938132</v>
+        <v>117940890</v>
       </c>
       <c r="B56" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7050,7 +6673,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7065,14 +6688,14 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>692562</v>
+        <v>692459</v>
       </c>
       <c r="R56" t="n">
-        <v>6635932</v>
+        <v>6635787</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7131,15 +6754,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117937938</v>
+        <v>117941471</v>
       </c>
       <c r="B57" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7166,7 +6784,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7176,17 +6794,17 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>692549</v>
+        <v>692463</v>
       </c>
       <c r="R57" t="n">
-        <v>6635965</v>
+        <v>6635816</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7215,7 +6833,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7225,7 +6843,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7252,50 +6870,59 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117941342</v>
+        <v>117941588</v>
       </c>
       <c r="B58" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>692449</v>
+        <v>692530</v>
       </c>
       <c r="R58" t="n">
-        <v>6635786</v>
+        <v>6635831</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7325,19 +6952,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7352,62 +6969,66 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117941484</v>
+        <v>117941596</v>
       </c>
       <c r="B59" t="n">
-        <v>90522</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>692520</v>
+        <v>692474</v>
       </c>
       <c r="R59" t="n">
-        <v>6635829</v>
+        <v>6635824</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7437,9 +7058,19 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7454,27 +7085,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117937757</v>
+        <v>117941641</v>
       </c>
       <c r="B60" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7501,7 +7127,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7511,19 +7137,19 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>692596</v>
+        <v>692543</v>
       </c>
       <c r="R60" t="n">
-        <v>6635955</v>
+        <v>6635857</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7582,15 +7208,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117941752</v>
+        <v>117941678</v>
       </c>
       <c r="B61" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7617,7 +7238,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7625,21 +7246,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>692560</v>
+        <v>692496</v>
       </c>
       <c r="R61" t="n">
-        <v>6635889</v>
+        <v>6635822</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7669,9 +7285,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7686,71 +7317,71 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117937862</v>
+        <v>117941687</v>
       </c>
       <c r="B62" t="n">
-        <v>5186</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>692594</v>
+        <v>692553</v>
       </c>
       <c r="R62" t="n">
-        <v>6635976</v>
+        <v>6635890</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7791,7 +7422,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7810,15 +7440,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117938078</v>
+        <v>117941752</v>
       </c>
       <c r="B63" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7845,7 +7470,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7860,14 +7485,14 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>692569</v>
+        <v>692560</v>
       </c>
       <c r="R63" t="n">
-        <v>6635939</v>
+        <v>6635889</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7926,59 +7551,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117940804</v>
+        <v>117941865</v>
       </c>
       <c r="B64" t="n">
-        <v>5186</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>692436</v>
+        <v>692513</v>
       </c>
       <c r="R64" t="n">
-        <v>6635782</v>
+        <v>6635854</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8008,85 +7628,103 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>En knoppig blomstängel</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117939070</v>
+        <v>117941966</v>
       </c>
       <c r="B65" t="n">
-        <v>5186</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>692498</v>
+        <v>692578</v>
       </c>
       <c r="R65" t="n">
-        <v>6635884</v>
+        <v>6635898</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8145,15 +7783,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117937256</v>
+        <v>117942036</v>
       </c>
       <c r="B66" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8180,7 +7813,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8195,14 +7828,14 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Sjöstugan), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>692608</v>
+        <v>692568</v>
       </c>
       <c r="R66" t="n">
-        <v>6635981</v>
+        <v>6635907</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8261,59 +7894,59 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117940793</v>
+        <v>117942075</v>
       </c>
       <c r="B67" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>692434</v>
+        <v>692570</v>
       </c>
       <c r="R67" t="n">
-        <v>6635779</v>
+        <v>6635906</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8354,7 +7987,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8373,50 +8005,54 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117941737</v>
+        <v>117942112</v>
       </c>
       <c r="B68" t="n">
-        <v>100107</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog S om Gäddsjön, Barrnaturskog S om Gäddsjön, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>692563</v>
+        <v>692538</v>
       </c>
       <c r="R68" t="n">
-        <v>6635887</v>
+        <v>6635877</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8446,9 +8082,24 @@
           <t>2024-06-22</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-06-22</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8463,65 +8114,74 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117942921</v>
+        <v>117942210</v>
       </c>
       <c r="B69" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön, Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>692583</v>
+        <v>692602</v>
       </c>
       <c r="R69" t="n">
-        <v>6635986</v>
+        <v>6635953</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8548,19 +8208,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>15:13</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8575,62 +8225,71 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117938005</v>
+        <v>117942312</v>
       </c>
       <c r="B70" t="n">
-        <v>57771</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103018</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>692578</v>
+        <v>692611</v>
       </c>
       <c r="R70" t="n">
-        <v>6635954</v>
+        <v>6635972</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8689,62 +8348,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117938311</v>
+        <v>117941737</v>
       </c>
       <c r="B71" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Barrnaturskog S om Gäddsjön (Barrnaturskog S om Gäddsjön), Upl</t>
+          <t>Barrnaturskog söder om Gäddsjön , Barrnaturskog söder om Gäddsjön , Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>692539</v>
+        <v>692563</v>
       </c>
       <c r="R71" t="n">
-        <v>6635922</v>
+        <v>6635887</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8771,24 +8416,9 @@
           <t>2024-06-22</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>En knoppig blomstängel</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8803,243 +8433,15 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>117942210</v>
-      </c>
-      <c r="B72" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>692602</v>
-      </c>
-      <c r="R72" t="n">
-        <v>6635953</v>
-      </c>
-      <c r="S72" t="n">
-        <v>10</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Norrtälje</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Edsbro</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>117985443</v>
-      </c>
-      <c r="B73" t="n">
-        <v>90518</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Barrnaturskog söder om Gäddsjön  (Barrnaturskog söder om Gäddsjön ), Upl</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>692541</v>
-      </c>
-      <c r="R73" t="n">
-        <v>6635891</v>
-      </c>
-      <c r="S73" t="n">
-        <v>25</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Norrtälje</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Edsbro</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2024-06-22</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20722-2024 artfynd.xlsx
+++ b/artfynd/A 20722-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AZ71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941899</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117985443</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
           <t>Skogsgruppen, RNF</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68600728</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941122</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,6 +1208,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937975</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1285,6 +1315,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938026</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1387,6 +1422,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117939282</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1489,6 +1529,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117939581</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1591,6 +1636,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941545</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1693,6 +1743,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117939062</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1800,6 +1855,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117940793</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1907,6 +1967,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941342</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2014,6 +2079,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117942921</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2111,6 +2181,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938005</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2218,6 +2293,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937862</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2320,6 +2400,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117939070</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2427,6 +2512,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117939646</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2534,6 +2624,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117940804</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2645,6 +2740,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937214</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2756,6 +2856,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937256</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2877,6 +2982,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937309</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2993,6 +3103,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937314</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3109,6 +3224,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937381</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3230,6 +3350,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937494</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3341,6 +3466,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937555</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3462,6 +3592,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937556</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3573,6 +3708,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937630</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3689,6 +3829,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937690</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3800,6 +3945,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937757</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3926,6 +4076,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937784</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4037,6 +4192,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937927</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4153,6 +4313,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937938</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4264,6 +4429,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937992</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4380,6 +4550,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117937995</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4491,6 +4666,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938078</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4602,6 +4782,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938132</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4713,6 +4898,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938174</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4834,6 +5024,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938213</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4945,6 +5140,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938225</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5066,6 +5266,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938311</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5182,6 +5387,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938431</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5298,6 +5508,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938580</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5409,6 +5624,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938588</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5520,6 +5740,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938661</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5631,6 +5856,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938795</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5742,6 +5972,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938933</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5853,6 +6088,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117938975</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5964,6 +6204,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117939029</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6075,6 +6320,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117939088</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6191,6 +6441,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117939183</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6302,6 +6557,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117939187</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6413,6 +6673,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117939212</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6529,6 +6794,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117939275</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6640,6 +6910,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117939382</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6751,6 +7026,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117940890</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6867,6 +7147,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941471</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6978,6 +7263,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941588</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7094,6 +7384,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941596</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7205,6 +7500,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941641</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7326,6 +7626,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941678</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7437,6 +7742,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941687</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7548,6 +7858,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941752</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7669,6 +7984,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941865</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7780,6 +8100,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941966</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7891,6 +8216,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117942036</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8002,6 +8332,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117942075</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8123,6 +8458,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117942112</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8234,6 +8574,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117942210</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8345,6 +8690,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117942312</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8442,8 +8792,85 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117941737</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>